--- a/08_results/primary_studies/primary_studies.xlsx
+++ b/08_results/primary_studies/primary_studies.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="134">
   <si>
     <t>#id</t>
   </si>
@@ -301,175 +301,109 @@
     <t>S20</t>
   </si>
   <si>
-    <t>Towards a semantically useful definition of conformance with a reference model</t>
-  </si>
-  <si>
-    <t>KONERSMANN, Marco.</t>
-  </si>
-  <si>
-    <t>10.5381/jot.2024.23.3.a5</t>
+    <t>Evolution and anti-patterns visualized: Microprospect in microservice architecture</t>
+  </si>
+  <si>
+    <t>ADAMS, Lauren et al.</t>
+  </si>
+  <si>
+    <t>10.1007/978-3-031-66326-0_19</t>
   </si>
   <si>
     <t>S21</t>
   </si>
   <si>
-    <t>Evolution and anti-patterns visualized: Microprospect in microservice architecture</t>
-  </si>
-  <si>
-    <t>ADAMS, Lauren et al.</t>
-  </si>
-  <si>
-    <t>10.1007/978-3-031-66326-0_19</t>
+    <t>Towards the detection of microservice patterns based on metrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL, João et al. </t>
+  </si>
+  <si>
+    <t>10.1109/SEAA60479.2023.00029</t>
   </si>
   <si>
     <t>S22</t>
   </si>
   <si>
-    <t>Towards the detection of microservice patterns based on metrics.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANIEL, João et al. </t>
-  </si>
-  <si>
-    <t>10.1109/SEAA60479.2023.00029</t>
+    <t>Detecting and Resolving Coupling-Related Infrastructure as Code Based Architecture Smells in Microservice Deployments</t>
+  </si>
+  <si>
+    <t>10.1109/CLOUD60044.2023.00031</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85174302755&amp;doi=10.1109%2FCLOUD60044.2023.00031&amp;partnerID=40&amp;md5=c14bcce16ca5f1ab642cef5a88458038</t>
   </si>
   <si>
     <t>S23</t>
   </si>
   <si>
-    <t>Extracting the Architecture of Microservices: An Approach for Explainability and Traceability</t>
-  </si>
-  <si>
-    <t>Queval, Pierre Jean and Zdun, Uwe</t>
-  </si>
-  <si>
-    <t>10.1007/978-3-031-42592-9_24</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85172069966&amp;doi=10.1007%2F978-3-031-42592-9_24&amp;partnerID=40&amp;md5=0a4509fefe26e4240984deaa4b0a70d1</t>
+    <t>A Toolchain for Checking Domain-and Model-Driven Properties of Jolie Microservices</t>
+  </si>
+  <si>
+    <t>GIALLORENZO, Saverio et al.</t>
+  </si>
+  <si>
+    <t>10.1007/978-981-96-0808-9_13</t>
   </si>
   <si>
     <t>S24</t>
   </si>
   <si>
-    <t>Detecting and Resolving Coupling-Related Infrastructure as Code Based Architecture Smells in Microservice Deployments</t>
-  </si>
-  <si>
-    <t>10.1109/CLOUD60044.2023.00031</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85174302755&amp;doi=10.1109%2FCLOUD60044.2023.00031&amp;partnerID=40&amp;md5=c14bcce16ca5f1ab642cef5a88458038</t>
+    <t>Detecting inconsistencies in microservice-based systems: An annotation-assisted scenario-oriented approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUN, Chang-Ai et al. </t>
+  </si>
+  <si>
+    <t>10.1109/TSC.2024.3399652</t>
   </si>
   <si>
     <t>S25</t>
   </si>
   <si>
-    <t>A Toolchain for Checking Domain-and Model-Driven Properties of Jolie Microservices</t>
-  </si>
-  <si>
-    <t>GIALLORENZO, Saverio et al.</t>
-  </si>
-  <si>
-    <t>10.1007/978-981-96-0808-9_13</t>
+    <t>DOMICO: Checking conformance between domain models and implementations</t>
+  </si>
+  <si>
+    <t>Zhong, Chenxing and Zhang, He and Huang, Huang and Chen, Zhikun and Li, Chao and Liu, Xiaodong and Li, Shanshan</t>
+  </si>
+  <si>
+    <t>10.1002/spe.3272</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85174190323&amp;doi=10.1002%2Fspe.3272&amp;partnerID=40&amp;md5=77117fcaf4d7e21b10d8ffbc4c176c19</t>
   </si>
   <si>
     <t>S26</t>
   </si>
   <si>
-    <t>Detecting inconsistencies in microservice-based systems: An annotation-assisted scenario-oriented approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUN, Chang-Ai et al. </t>
-  </si>
-  <si>
-    <t>10.1109/TSC.2024.3399652</t>
+    <t>Detection Strategies for Microservice Security Tactics</t>
+  </si>
+  <si>
+    <t>Zdun, Uwe and Queval, Pierre Jean and Simhandl, Georg and Scandariato, Riccardo and Chakravarty, Somik and Jelić, Marjan and Jovanović, A. S.</t>
+  </si>
+  <si>
+    <t>10.1109/TDSC.2023.3276487</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85160216527&amp;doi=10.1109%2FTDSC.2023.3276487&amp;partnerID=40&amp;md5=9c14d9de24c27f20d68ba619a574a65d</t>
   </si>
   <si>
     <t>S27</t>
   </si>
   <si>
-    <t>Assessing evolution of microservices using static analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABDELFATTAH, Amr S. et al. </t>
-  </si>
-  <si>
-    <t>10.3390/app142210725</t>
+    <t>CATMA: Conformance Analysis Tool for Microservice Applications</t>
+  </si>
+  <si>
+    <t>Cao, Clinton and Schneider, Simon and Díaz Ferreyra, Nicolás E. and Verwer, Sicco E. and Panichella, Annibale and Scandariato, Riccardo</t>
+  </si>
+  <si>
+    <t>10.1145/3639478.3640022</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85188258629&amp;doi=10.1145%2F3639478.3640022&amp;partnerID=40&amp;md5=1f4f18ceba149d26d74bb010a0657fb2</t>
   </si>
   <si>
     <t>S28</t>
-  </si>
-  <si>
-    <t>Exploring Architectural Evolution in Microservice Systems Using Repository Mining Techniques and Static Code Analysis</t>
-  </si>
-  <si>
-    <t>Genfer, Patric and Zdun, Uwe</t>
-  </si>
-  <si>
-    <t>10.1007/978-3-031-70797-1_10</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85203600424&amp;doi=10.1007%2F978-3-031-70797-1_10&amp;partnerID=40&amp;md5=7a0d70dcf9868757ca1f21ec1cf1b792</t>
-  </si>
-  <si>
-    <t>S29</t>
-  </si>
-  <si>
-    <t>DOMICO: Checking conformance between domain models and implementations</t>
-  </si>
-  <si>
-    <t>Zhong, Chenxing and Zhang, He and Huang, Huang and Chen, Zhikun and Li, Chao and Liu, Xiaodong and Li, Shanshan</t>
-  </si>
-  <si>
-    <t>10.1002/spe.3272</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85174190323&amp;doi=10.1002%2Fspe.3272&amp;partnerID=40&amp;md5=77117fcaf4d7e21b10d8ffbc4c176c19</t>
-  </si>
-  <si>
-    <t>S30</t>
-  </si>
-  <si>
-    <t>Detection Strategies for Microservice Security Tactics</t>
-  </si>
-  <si>
-    <t>Zdun, Uwe and Queval, Pierre Jean and Simhandl, Georg and Scandariato, Riccardo and Chakravarty, Somik and Jelić, Marjan and Jovanović, A. S.</t>
-  </si>
-  <si>
-    <t>10.1109/TDSC.2023.3276487</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85160216527&amp;doi=10.1109%2FTDSC.2023.3276487&amp;partnerID=40&amp;md5=9c14d9de24c27f20d68ba619a574a65d</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>CATMA: Conformance Analysis Tool for Microservice Applications</t>
-  </si>
-  <si>
-    <t>Cao, Clinton and Schneider, Simon and Díaz Ferreyra, Nicolás E. and Verwer, Sicco E. and Panichella, Annibale and Scandariato, Riccardo</t>
-  </si>
-  <si>
-    <t>10.1145/3639478.3640022</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85188258629&amp;doi=10.1145%2F3639478.3640022&amp;partnerID=40&amp;md5=1f4f18ceba149d26d74bb010a0657fb2</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>Continuous Conformance of Software Architectures</t>
-  </si>
-  <si>
-    <t>Bucaioni, Alessio and Di Salle, Amleto and Iovino, Ludovico and Mariani, Leonardo and Pelliccione, Patrizio</t>
-  </si>
-  <si>
-    <t>10.1109/ICSA59870.2024.00019</t>
-  </si>
-  <si>
-    <t>S33</t>
   </si>
   <si>
     <t>Semantic dependency in microservice architecture.</t>
@@ -525,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -555,9 +489,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1246,7 +1177,7 @@
       <c r="E21" s="6">
         <v>2023.0</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1274,19 +1205,22 @@
       <c r="A23" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>19</v>
+      <c r="B23" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>105</v>
+      <c r="D23" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="E23" s="6">
         <v>2023.0</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1294,65 +1228,62 @@
       <c r="A24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>8</v>
+      <c r="B24" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>109</v>
       </c>
       <c r="E24" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="F24" s="5" t="s">
+        <v>2024.0</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="E25" s="6">
-        <v>2023.0</v>
-      </c>
-      <c r="F25" s="5" t="s">
+        <v>2024.0</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="E26" s="6">
         <v>2024.0</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1360,173 +1291,66 @@
       <c r="A27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>19</v>
+      <c r="B27" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E27" s="6">
         <v>2024.0</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="5" t="s">
         <v>123</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>126</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="E28" s="6">
         <v>2024.0</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>127</v>
+      <c r="F28" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>130</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="E29" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+        <v>2025.0</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E31" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G33" s="10"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
